--- a/outputs/monitor_xlsx/20260211.xlsx
+++ b/outputs/monitor_xlsx/20260211.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2388,13 +2388,13 @@
         <v>717</v>
       </c>
       <c r="L24" t="n">
-        <v>4437</v>
+        <v>3539</v>
       </c>
       <c r="M24" t="n">
         <v>-106283</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2452,6 +2452,59 @@
       <c r="O25" t="inlineStr">
         <is>
           <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5005</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E26" t="n">
+        <v>384</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-97</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>48</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>339</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1648</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-8884</v>
+      </c>
+      <c r="N26" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260211.xlsx
+++ b/outputs/monitor_xlsx/20260211.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1113,40 +1116,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1204,12 +1202,7 @@
       <c r="O4" t="n">
         <v>5.39</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1247,12 +1240,7 @@
       <c r="N5" t="n">
         <v>-28650</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1310,12 +1298,7 @@
       <c r="O6" t="n">
         <v>1.43</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1373,12 +1356,7 @@
       <c r="O7" t="n">
         <v>7.05</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1436,12 +1414,7 @@
       <c r="O8" t="n">
         <v>6.09</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1499,12 +1472,7 @@
       <c r="O9" t="n">
         <v>1.48</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1562,12 +1530,7 @@
       <c r="O10" t="n">
         <v>8.66</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1625,12 +1588,7 @@
       <c r="O11" t="n">
         <v>3.49</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1688,12 +1646,7 @@
       <c r="O12" t="n">
         <v>-4.61</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1751,12 +1704,7 @@
       <c r="O13" t="n">
         <v>6.62</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1814,12 +1762,7 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1877,12 +1820,7 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1937,12 +1875,7 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2000,12 +1933,7 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2063,12 +1991,7 @@
       <c r="O18" t="n">
         <v>3.31</v>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2126,12 +2049,7 @@
       <c r="O19" t="n">
         <v>2.47</v>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/outputs/monitor_xlsx/20260211.xlsx
+++ b/outputs/monitor_xlsx/20260211.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2426,6 +2423,51 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10013</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7980</v>
+      </c>
+      <c r="H27" t="n">
+        <v>95</v>
+      </c>
+      <c r="I27" t="n">
+        <v>475</v>
+      </c>
+      <c r="J27" t="n">
+        <v>272</v>
+      </c>
+      <c r="K27" t="n">
+        <v>6004</v>
+      </c>
+      <c r="L27" t="n">
+        <v>11851</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-21379</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/outputs/monitor_xlsx/20260211.xlsx
+++ b/outputs/monitor_xlsx/20260211.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1163,26 +1163,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>77.2</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2.25</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>120639</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1195</v>
       </c>
       <c r="H4" t="n">
-        <v>-31467</v>
+        <v>-14398</v>
       </c>
       <c r="I4" t="n">
         <v>8500</v>
       </c>
       <c r="J4" t="n">
-        <v>10926</v>
+        <v>17326</v>
       </c>
       <c r="K4" t="n">
         <v>36762</v>
@@ -1191,13 +1191,13 @@
         <v>7374</v>
       </c>
       <c r="M4" t="n">
-        <v>37778</v>
+        <v>37522</v>
       </c>
       <c r="N4" t="n">
         <v>-4047132</v>
       </c>
       <c r="O4" t="n">
-        <v>5.39</v>
+        <v>5.93</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1259,26 +1259,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>967</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>4085</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>722</v>
       </c>
       <c r="H6" t="n">
-        <v>37</v>
+        <v>849</v>
       </c>
       <c r="I6" t="n">
         <v>-596</v>
       </c>
       <c r="J6" t="n">
-        <v>120</v>
+        <v>-516</v>
       </c>
       <c r="K6" t="n">
         <v>90</v>
@@ -1287,13 +1287,13 @@
         <v>2838</v>
       </c>
       <c r="M6" t="n">
-        <v>14359</v>
+        <v>14376</v>
       </c>
       <c r="N6" t="n">
         <v>-78751</v>
       </c>
       <c r="O6" t="n">
-        <v>1.43</v>
+        <v>-1.62</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1317,26 +1317,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1260</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>6.33</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>15443</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1446</v>
       </c>
       <c r="H7" t="n">
-        <v>-6864</v>
+        <v>-6530</v>
       </c>
       <c r="I7" t="n">
         <v>684</v>
       </c>
       <c r="J7" t="n">
-        <v>564</v>
+        <v>1169</v>
       </c>
       <c r="K7" t="n">
         <v>360</v>
@@ -1345,13 +1345,13 @@
         <v>6443</v>
       </c>
       <c r="M7" t="n">
-        <v>30522</v>
+        <v>30813</v>
       </c>
       <c r="N7" t="n">
         <v>-648658</v>
       </c>
       <c r="O7" t="n">
-        <v>7.05</v>
+        <v>5.75</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1375,26 +1375,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1915</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1.86</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>44684</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>-4941</v>
       </c>
       <c r="H8" t="n">
-        <v>-10335</v>
+        <v>-5631</v>
       </c>
       <c r="I8" t="n">
         <v>1141</v>
       </c>
       <c r="J8" t="n">
-        <v>3546</v>
+        <v>3847</v>
       </c>
       <c r="K8" t="n">
         <v>345</v>
@@ -1403,13 +1403,13 @@
         <v>21275</v>
       </c>
       <c r="M8" t="n">
-        <v>112536</v>
+        <v>111537</v>
       </c>
       <c r="N8" t="n">
         <v>-6482864</v>
       </c>
       <c r="O8" t="n">
-        <v>6.09</v>
+        <v>7.36</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1491,26 +1491,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2195</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>4.28</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>5309</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>-1205</v>
       </c>
       <c r="H10" t="n">
-        <v>-369</v>
+        <v>-2642</v>
       </c>
       <c r="I10" t="n">
         <v>884</v>
       </c>
       <c r="J10" t="n">
-        <v>1349</v>
+        <v>2065</v>
       </c>
       <c r="K10" t="n">
         <v>108</v>
@@ -1519,13 +1519,13 @@
         <v>2228</v>
       </c>
       <c r="M10" t="n">
-        <v>10715</v>
+        <v>10783</v>
       </c>
       <c r="N10" t="n">
         <v>-89475</v>
       </c>
       <c r="O10" t="n">
-        <v>8.66</v>
+        <v>20.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1665,26 +1665,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="7" t="n">
         <v>1950</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>-1.76</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="7" t="n">
         <v>1008</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>52</v>
       </c>
       <c r="H13" t="n">
-        <v>398</v>
+        <v>517</v>
       </c>
       <c r="I13" t="n">
         <v>-5</v>
       </c>
       <c r="J13" t="n">
-        <v>-64</v>
+        <v>-86</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
@@ -1693,13 +1693,13 @@
         <v>4113</v>
       </c>
       <c r="M13" t="n">
-        <v>21693</v>
+        <v>21377</v>
       </c>
       <c r="N13" t="n">
         <v>-19217</v>
       </c>
       <c r="O13" t="n">
-        <v>6.62</v>
+        <v>24.11</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1713,36 +1713,28 @@
           <t>3081</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1375</v>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" s="6" t="n">
+        <v>2.16</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1830</v>
+        <v>2182</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-92</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-92</v>
       </c>
       <c r="H14" t="n">
-        <v>516</v>
+        <v>319</v>
       </c>
       <c r="I14" t="n">
         <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>-30</v>
+        <v>33</v>
       </c>
       <c r="K14" t="n">
         <v>19</v>
@@ -1751,7 +1743,7 @@
         <v>-8</v>
       </c>
       <c r="M14" t="n">
-        <v>-416</v>
+        <v>-374</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1884,36 +1876,28 @@
           <t>4979</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>華星光</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>462.5</v>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" s="6" t="n">
+        <v>9.94</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="F17" t="n">
-        <v>26137</v>
+        <v>32773</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-1023</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>-1023</v>
       </c>
       <c r="H17" t="n">
-        <v>1869</v>
+        <v>-1049</v>
       </c>
       <c r="I17" t="n">
         <v>-47</v>
       </c>
       <c r="J17" t="n">
-        <v>3198</v>
+        <v>2385</v>
       </c>
       <c r="K17" t="n">
         <v>-198</v>
@@ -1922,7 +1906,7 @@
         <v>-561</v>
       </c>
       <c r="M17" t="n">
-        <v>-878</v>
+        <v>-1637</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2116,46 +2100,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
         <v>1450</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="E21" s="6" t="n">
         <v>4.32</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" s="7" t="n">
         <v>7612</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="G21" s="7" t="n">
         <v>666</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>3446</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>306</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>1751</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>202</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>2053</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>11934</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>-140135</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>20.71</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -2164,43 +2148,37 @@
           <t>6640</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>962</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" s="7" t="n">
-        <v>-0.1</v>
+        <v>-6.07</v>
       </c>
       <c r="E22" t="n">
-        <v>826</v>
+        <v>1168</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="H22" t="n">
         <v>10</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>-18</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>3</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-62</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-65</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2217,43 +2195,37 @@
           <t>6187</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>624</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>6.48</v>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" s="7" t="n">
+        <v>-2.64</v>
       </c>
       <c r="E23" t="n">
-        <v>2040</v>
+        <v>6341</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>823</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="7" t="n">
+        <v>823</v>
+      </c>
+      <c r="H23" t="n">
         <v>1143</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>-32</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>-77</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>-141</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2275,46 +2247,46 @@
           <t>致茂</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
         <v>1050</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="E24" s="6" t="n">
         <v>0.96</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" s="7" t="n">
         <v>1687</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="G24" s="7" t="n">
         <v>267</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>543</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>-51</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>-289</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>77</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>717</v>
       </c>
-      <c r="L24" t="n">
-        <v>3539</v>
-      </c>
       <c r="M24" t="n">
+        <v>4437</v>
+      </c>
+      <c r="N24" t="n">
         <v>-106283</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
+      <c r="O24" t="n">
+        <v>4.23</v>
       </c>
     </row>
     <row r="25">
@@ -2381,46 +2353,46 @@
           <t>穎崴</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
         <v>5005</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>2.25</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" s="6" t="n">
         <v>384</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="6" t="n">
         <v>-18</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-97</v>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
       <c r="I26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J26" t="n">
         <v>48</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>3</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>339</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>1648</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>-8884</v>
       </c>
-      <c r="N26" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
+      <c r="O26" t="n">
+        <v>21.39</v>
       </c>
     </row>
     <row r="27">
@@ -2434,38 +2406,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
         <v>271.5</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="E27" s="7" t="n">
         <v>-1.45</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" s="7" t="n">
         <v>10013</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="G27" s="7" t="n">
         <v>156</v>
       </c>
-      <c r="G27" t="n">
-        <v>7980</v>
-      </c>
       <c r="H27" t="n">
+        <v>12299</v>
+      </c>
+      <c r="I27" t="n">
         <v>95</v>
       </c>
-      <c r="I27" t="n">
-        <v>475</v>
-      </c>
       <c r="J27" t="n">
+        <v>449</v>
+      </c>
+      <c r="K27" t="n">
         <v>272</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>6004</v>
       </c>
-      <c r="L27" t="n">
-        <v>11851</v>
-      </c>
       <c r="M27" t="n">
+        <v>30441</v>
+      </c>
+      <c r="N27" t="n">
         <v>-21379</v>
+      </c>
+      <c r="O27" t="n">
+        <v>18.77</v>
       </c>
     </row>
   </sheetData>
